--- a/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info[Mod道具信息].xlsx
+++ b/DemonLordRoguelikeMod/Assets/Data/Excel/excel_mod_items_info[Mod道具信息].xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>形象键值串:show段(show_res:X&amp;show_data:scale;x,y)与ui_show段(ui_show_res:X&amp;ui_show_data:scale;x,y)至少一段,可选world_data:scale;x,y(&amp;拆项,:拆键值,缺省键省略)</t>
+          <t>形象键值串:show段(show_res:X&amp;show_data:scale;x,y)与ui_show段(ui_show_res:X&amp;ui_show_data:scale;x,y)至少一段,可选world_data:scale;x,y、idle_anim/ui_show_idle_anim:动画名(无标准idle时的替代待机动画)(&amp;拆项,:拆键值,缺省键省略)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -16406,7 +16406,7 @@
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr">
         <is>
-          <t>ui_show_res:6001_Elf_SkeletonData&amp;ui_show_data:0.1828;0,0</t>
+          <t>ui_show_res:6001_Elf_SkeletonData&amp;ui_show_data:0.1828;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K332" t="n">
@@ -16454,7 +16454,7 @@
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr">
         <is>
-          <t>ui_show_res:6002_Elf_SkeletonData&amp;ui_show_data:0.1762;0,0</t>
+          <t>ui_show_res:6002_Elf_SkeletonData&amp;ui_show_data:0.1762;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K333" t="n">
@@ -16502,7 +16502,7 @@
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr">
         <is>
-          <t>ui_show_res:6003_Elf_SkeletonData&amp;ui_show_data:0.195;0,0</t>
+          <t>ui_show_res:6003_Elf_SkeletonData&amp;ui_show_data:0.195;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K334" t="n">
@@ -16550,7 +16550,7 @@
       <c r="I335" t="inlineStr"/>
       <c r="J335" t="inlineStr">
         <is>
-          <t>ui_show_res:6004_Elf_SkeletonData&amp;ui_show_data:0.204;0,0</t>
+          <t>ui_show_res:6004_Elf_SkeletonData&amp;ui_show_data:0.204;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K335" t="n">
@@ -16598,7 +16598,7 @@
       <c r="I336" t="inlineStr"/>
       <c r="J336" t="inlineStr">
         <is>
-          <t>ui_show_res:6005_Elf_SkeletonData&amp;ui_show_data:0.2007;0,0</t>
+          <t>ui_show_res:6005_Elf_SkeletonData&amp;ui_show_data:0.2007;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K336" t="n">
@@ -16646,7 +16646,7 @@
       <c r="I337" t="inlineStr"/>
       <c r="J337" t="inlineStr">
         <is>
-          <t>ui_show_res:6006_Elf_SkeletonData&amp;ui_show_data:0.1649;0,0</t>
+          <t>ui_show_res:6006_Elf_SkeletonData&amp;ui_show_data:0.1649;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K337" t="n">
@@ -16694,7 +16694,7 @@
       <c r="I338" t="inlineStr"/>
       <c r="J338" t="inlineStr">
         <is>
-          <t>ui_show_res:6007_Elf_SkeletonData&amp;ui_show_data:0.2275;0,0</t>
+          <t>ui_show_res:6007_Elf_SkeletonData&amp;ui_show_data:0.2275;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K338" t="n">
@@ -16742,7 +16742,7 @@
       <c r="I339" t="inlineStr"/>
       <c r="J339" t="inlineStr">
         <is>
-          <t>ui_show_res:6008_Elf_SkeletonData&amp;ui_show_data:0.2045;0,0</t>
+          <t>ui_show_res:6008_Elf_SkeletonData&amp;ui_show_data:0.2045;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K339" t="n">
@@ -16790,7 +16790,7 @@
       <c r="I340" t="inlineStr"/>
       <c r="J340" t="inlineStr">
         <is>
-          <t>ui_show_res:6009_Elf_SkeletonData&amp;ui_show_data:0.227;0,0</t>
+          <t>ui_show_res:6009_Elf_SkeletonData&amp;ui_show_data:0.227;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K340" t="n">
@@ -16838,7 +16838,7 @@
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr">
         <is>
-          <t>ui_show_res:6010_Elf_SkeletonData&amp;ui_show_data:0.1765;0,0</t>
+          <t>ui_show_res:6010_Elf_SkeletonData&amp;ui_show_data:0.1765;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K341" t="n">
@@ -16886,7 +16886,7 @@
       <c r="I342" t="inlineStr"/>
       <c r="J342" t="inlineStr">
         <is>
-          <t>ui_show_res:6011_Elf_SkeletonData&amp;ui_show_data:0.2012;0,0</t>
+          <t>ui_show_res:6011_Elf_SkeletonData&amp;ui_show_data:0.2012;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K342" t="n">
@@ -16934,7 +16934,7 @@
       <c r="I343" t="inlineStr"/>
       <c r="J343" t="inlineStr">
         <is>
-          <t>ui_show_res:6012_Elf_SkeletonData&amp;ui_show_data:0.149;0,0</t>
+          <t>ui_show_res:6012_Elf_SkeletonData&amp;ui_show_data:0.149;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K343" t="n">
@@ -16982,7 +16982,7 @@
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr">
         <is>
-          <t>ui_show_res:6013_Elf_SkeletonData&amp;ui_show_data:0.1825;0,0</t>
+          <t>ui_show_res:6013_Elf_SkeletonData&amp;ui_show_data:0.1825;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K344" t="n">
@@ -17030,7 +17030,7 @@
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr">
         <is>
-          <t>ui_show_res:6014_Elf_SkeletonData&amp;ui_show_data:0.1795;0,0</t>
+          <t>ui_show_res:6014_Elf_SkeletonData&amp;ui_show_data:0.1795;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K345" t="n">
@@ -17078,7 +17078,7 @@
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr">
         <is>
-          <t>ui_show_res:6015_Elf_SkeletonData&amp;ui_show_data:0.1673;0,0</t>
+          <t>ui_show_res:6015_Elf_SkeletonData&amp;ui_show_data:0.1673;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K346" t="n">
@@ -17126,7 +17126,7 @@
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr">
         <is>
-          <t>ui_show_res:6016_Elf_SkeletonData&amp;ui_show_data:0.1837;0,0</t>
+          <t>ui_show_res:6016_Elf_SkeletonData&amp;ui_show_data:0.1837;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K347" t="n">
@@ -17174,7 +17174,7 @@
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr">
         <is>
-          <t>ui_show_res:6017_Elf_SkeletonData&amp;ui_show_data:0.1687;0,0</t>
+          <t>ui_show_res:6017_Elf_SkeletonData&amp;ui_show_data:0.1687;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K348" t="n">
@@ -17222,7 +17222,7 @@
       <c r="I349" t="inlineStr"/>
       <c r="J349" t="inlineStr">
         <is>
-          <t>ui_show_res:6018_Elf_SkeletonData&amp;ui_show_data:0.1493;0,0</t>
+          <t>ui_show_res:6018_Elf_SkeletonData&amp;ui_show_data:0.1493;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K349" t="n">
@@ -17270,7 +17270,7 @@
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr">
         <is>
-          <t>ui_show_res:6019_Elf_SkeletonData&amp;ui_show_data:0.141;0,0</t>
+          <t>ui_show_res:6019_Elf_SkeletonData&amp;ui_show_data:0.141;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K350" t="n">
@@ -17318,7 +17318,7 @@
       <c r="I351" t="inlineStr"/>
       <c r="J351" t="inlineStr">
         <is>
-          <t>ui_show_res:6020_Elf_SkeletonData&amp;ui_show_data:0.1919;0,0</t>
+          <t>ui_show_res:6020_Elf_SkeletonData&amp;ui_show_data:0.1919;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K351" t="n">
@@ -17366,7 +17366,7 @@
       <c r="I352" t="inlineStr"/>
       <c r="J352" t="inlineStr">
         <is>
-          <t>ui_show_res:6021_Elf_SkeletonData&amp;ui_show_data:0.1512;0,0</t>
+          <t>ui_show_res:6021_Elf_SkeletonData&amp;ui_show_data:0.1512;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K352" t="n">
@@ -17414,7 +17414,7 @@
       <c r="I353" t="inlineStr"/>
       <c r="J353" t="inlineStr">
         <is>
-          <t>ui_show_res:6022_Elf_SkeletonData&amp;ui_show_data:0.1485;0,0</t>
+          <t>ui_show_res:6022_Elf_SkeletonData&amp;ui_show_data:0.1485;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K353" t="n">
@@ -17462,7 +17462,7 @@
       <c r="I354" t="inlineStr"/>
       <c r="J354" t="inlineStr">
         <is>
-          <t>ui_show_res:6023_Elf_SkeletonData&amp;ui_show_data:0.1951;0,0</t>
+          <t>ui_show_res:6023_Elf_SkeletonData&amp;ui_show_data:0.1951;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K354" t="n">
@@ -17510,7 +17510,7 @@
       <c r="I355" t="inlineStr"/>
       <c r="J355" t="inlineStr">
         <is>
-          <t>ui_show_res:6024_Elf_SkeletonData&amp;ui_show_data:0.1919;0,0</t>
+          <t>ui_show_res:6024_Elf_SkeletonData&amp;ui_show_data:0.1919;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K355" t="n">
@@ -17558,7 +17558,7 @@
       <c r="I356" t="inlineStr"/>
       <c r="J356" t="inlineStr">
         <is>
-          <t>ui_show_res:6025_Elf_SkeletonData&amp;ui_show_data:0.231;0,0</t>
+          <t>ui_show_res:6025_Elf_SkeletonData&amp;ui_show_data:0.231;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K356" t="n">
@@ -17606,7 +17606,7 @@
       <c r="I357" t="inlineStr"/>
       <c r="J357" t="inlineStr">
         <is>
-          <t>ui_show_res:6026_Elf_SkeletonData&amp;ui_show_data:0.2124;0,0</t>
+          <t>ui_show_res:6026_Elf_SkeletonData&amp;ui_show_data:0.2124;0,0&amp;ui_show_idle_anim:idle_emo1</t>
         </is>
       </c>
       <c r="K357" t="n">
